--- a/data/trans_orig/P6710-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6710-Clase-trans_orig.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede decidir cuándo hace un descanso en 2012</t>
+          <t>Población según si puede decidir cuándo hace un descanso en 2012 (tasa de respuesta: 98,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27113</t>
+          <t>26733</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>10095</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26873</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24481</t>
+          <t>25343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47392</t>
+          <t>48495</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30835</t>
+          <t>28927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12609</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31277</t>
+          <t>31252</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26701</t>
+          <t>26835</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51940</t>
+          <t>51873</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37522</t>
+          <t>38543</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66394</t>
+          <t>65802</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28173</t>
+          <t>28092</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52886</t>
+          <t>52315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73484</t>
+          <t>72923</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109782</t>
+          <t>110110</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54989</t>
+          <t>55316</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84501</t>
+          <t>86006</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>19057</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41692</t>
+          <t>39637</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82867</t>
+          <t>82720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120892</t>
+          <t>117742</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>129264</t>
+          <t>127992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>165105</t>
+          <t>163873</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72340</t>
+          <t>72987</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101253</t>
+          <t>102211</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209303</t>
+          <t>210618</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255325</t>
+          <t>255307</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,55%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>20379</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28606</t>
+          <t>28121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19268</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43318</t>
+          <t>44193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27891</t>
+          <t>28747</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22412</t>
+          <t>22017</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19892</t>
+          <t>20618</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43425</t>
+          <t>44486</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49138</t>
+          <t>49014</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>79091</t>
+          <t>78248</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29621</t>
+          <t>28887</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53522</t>
+          <t>51240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85170</t>
+          <t>82889</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>121748</t>
+          <t>120437</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49757</t>
+          <t>50828</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79266</t>
+          <t>79510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27788</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49347</t>
+          <t>50424</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85035</t>
+          <t>84666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120324</t>
+          <t>121997</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82005</t>
+          <t>82034</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117215</t>
+          <t>116715</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45450</t>
+          <t>44437</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70597</t>
+          <t>70568</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135727</t>
+          <t>134792</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177208</t>
+          <t>178510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>10292</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>28370</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15424</t>
+          <t>16073</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36042</t>
+          <t>37649</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24960</t>
+          <t>24344</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,82 +2223,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>12134</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>10,98%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>20496</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>13138</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>29498</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>3,37%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8,93%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>5176</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>11620</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>20496</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>13245</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>30862</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36576</t>
+          <t>36528</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62759</t>
+          <t>63291</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25874</t>
+          <t>26029</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50600</t>
+          <t>51492</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79820</t>
+          <t>81036</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43010</t>
+          <t>42608</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69424</t>
+          <t>68907</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19197</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51494</t>
+          <t>52206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81074</t>
+          <t>80826</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126798</t>
+          <t>126969</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>158325</t>
+          <t>160580</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60205</t>
+          <t>59686</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80766</t>
+          <t>80265</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>194643</t>
+          <t>193724</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>234289</t>
+          <t>232036</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,47%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47881</t>
+          <t>49319</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77930</t>
+          <t>79681</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38640</t>
+          <t>39001</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66019</t>
+          <t>65269</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94354</t>
+          <t>93368</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>135549</t>
+          <t>135140</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33413</t>
+          <t>34852</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60386</t>
+          <t>61177</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24340</t>
+          <t>25143</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48289</t>
+          <t>49158</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>64332</t>
+          <t>63519</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>99824</t>
+          <t>100937</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>81641</t>
+          <t>80209</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>120139</t>
+          <t>119379</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40484</t>
+          <t>41449</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>67414</t>
+          <t>68739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>129063</t>
+          <t>128998</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>174345</t>
+          <t>173921</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67014</t>
+          <t>65981</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>100124</t>
+          <t>100457</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56373</t>
+          <t>56355</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86791</t>
+          <t>86512</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130506</t>
+          <t>130558</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>176056</t>
+          <t>175468</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>113929</t>
+          <t>112007</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>151856</t>
+          <t>150867</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76192</t>
+          <t>75246</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>108170</t>
+          <t>108258</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>198286</t>
+          <t>196307</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>246283</t>
+          <t>249509</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39851</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20988</t>
+          <t>21479</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43788</t>
+          <t>41441</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>46055</t>
+          <t>45103</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>76445</t>
+          <t>74744</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24986</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27570</t>
+          <t>28734</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22669</t>
+          <t>24488</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46522</t>
+          <t>46776</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>24914</t>
+          <t>23810</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45896</t>
+          <t>45022</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19491</t>
+          <t>19039</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>39848</t>
+          <t>41107</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>50894</t>
+          <t>48309</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80221</t>
+          <t>77383</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41886</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>28898</t>
+          <t>28934</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52167</t>
+          <t>50982</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>55964</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>86477</t>
+          <t>87760</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>31953</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>53652</t>
+          <t>53649</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>43227</t>
+          <t>43154</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>71029</t>
+          <t>69396</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>80175</t>
+          <t>80407</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>115798</t>
+          <t>114364</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4131,107 +4131,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>129</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138589</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>114738</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>162582</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>122811</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>103443</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>145822</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>261400</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>231854</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>293419</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -4244,107 +4244,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>102</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112006</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90642</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135581</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91903</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74131</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112108</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>185</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>203909</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>176266</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234070</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -4357,107 +4357,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>274</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>293588</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>265133</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325211</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>164</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>177225</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>152244</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>203388</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>438</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>470813</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>433235</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>515575</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -4470,107 +4470,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>292</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>302099</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>269276</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333028</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>177</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>187902</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>162389</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>211832</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>469</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>490001</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>449582</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>533129</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -4583,107 +4583,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>528</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>563409</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>529498</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>602581</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>330</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>360716</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333069</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>393339</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>858</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>924125</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>876157</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>973936</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -4696,804 +4696,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1409691</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1409691</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1409691</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>868</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>940556</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>940556</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>940556</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2350247</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2350247</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2350247</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>138589</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>114556</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>164220</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>122811</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>100649</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>143729</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>13,06%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>10,7%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>15,28%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>261400</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>232853</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>298284</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>11,12%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>112006</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>92123</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>135760</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>91903</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>72394</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>112893</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>12,0%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>203909</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>175147</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>231292</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>293588</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>263089</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>323334</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>20,83%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>18,66%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>22,94%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>177225</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>153510</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>202693</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>18,84%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>16,32%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>470813</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>432261</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>511929</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>18,39%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>21,78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>302099</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>272158</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>335218</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>21,43%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>19,31%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>23,78%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>187902</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>164464</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>214331</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>19,98%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>17,49%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>22,79%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>490001</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>451391</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>533910</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>20,85%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>19,21%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>563409</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>525311</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>597471</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>39,97%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>37,26%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>42,38%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>360716</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>333239</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>391467</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>38,35%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>35,43%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>41,62%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>924125</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>879634</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>977402</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>39,32%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>37,43%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>41,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1325</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1409691</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1409691</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1409691</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>940556</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>940556</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>940556</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2193</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2350247</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2350247</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2350247</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>
@@ -5513,7 +4830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5544,7 +4861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede decidir cuándo hace un descanso en 2016</t>
+          <t>Población según si puede decidir cuándo hace un descanso en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5739,12 +5056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39949</t>
+          <t>39331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5754,12 +5071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5774,12 +5091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25213</t>
+          <t>25300</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46830</t>
+          <t>48470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5789,12 +5106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5809,12 +5126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49102</t>
+          <t>49254</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79646</t>
+          <t>79636</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5824,7 +5141,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5852,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19827</t>
+          <t>20576</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41232</t>
+          <t>41124</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5867,12 +5184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5887,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25232</t>
+          <t>24838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46679</t>
+          <t>48094</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5902,12 +5219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5922,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52431</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82316</t>
+          <t>81564</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5937,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62637</t>
+          <t>63211</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94750</t>
+          <t>94743</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5980,7 +5297,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -6000,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51630</t>
+          <t>51579</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77469</t>
+          <t>78227</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6015,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6035,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>122027</t>
+          <t>121920</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>164063</t>
+          <t>164651</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6050,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40934</t>
+          <t>40018</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67908</t>
+          <t>67507</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6093,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6113,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14708</t>
+          <t>15218</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32810</t>
+          <t>32185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6128,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6148,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59569</t>
+          <t>59501</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91780</t>
+          <t>91050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6163,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74197</t>
+          <t>74903</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107698</t>
+          <t>106833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6206,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6226,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44918</t>
+          <t>44257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>71333</t>
+          <t>71461</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6241,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6261,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>125014</t>
+          <t>125322</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168379</t>
+          <t>167030</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6276,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20005</t>
+          <t>20528</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40329</t>
+          <t>41401</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6436,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6456,12 +5773,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17239</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35973</t>
+          <t>36896</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6471,12 +5788,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6491,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42481</t>
+          <t>41831</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69809</t>
+          <t>72698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6506,12 +5823,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28018</t>
+          <t>28631</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52223</t>
+          <t>53243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6549,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6569,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24560</t>
+          <t>23695</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44548</t>
+          <t>44144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6584,12 +5901,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6604,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58783</t>
+          <t>56583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90803</t>
+          <t>89769</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6619,12 +5936,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50062</t>
+          <t>50547</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77048</t>
+          <t>79131</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6662,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6682,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37758</t>
+          <t>38850</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62934</t>
+          <t>63468</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6697,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6717,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96333</t>
+          <t>97282</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133269</t>
+          <t>133779</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6732,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39228</t>
+          <t>39321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64525</t>
+          <t>64450</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6775,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6795,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30361</t>
+          <t>30008</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52418</t>
+          <t>52351</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6810,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6830,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74845</t>
+          <t>75689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111104</t>
+          <t>110767</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6845,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47410</t>
+          <t>47951</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75556</t>
+          <t>74607</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6888,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6908,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27702</t>
+          <t>27829</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51578</t>
+          <t>50246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6923,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6943,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81921</t>
+          <t>81826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118878</t>
+          <t>117182</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6958,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23801</t>
+          <t>25039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7118,12 +6435,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7138,12 +6455,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>916</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7153,12 +6470,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7173,12 +6490,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28513</t>
+          <t>28290</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7188,12 +6505,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15286</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32762</t>
+          <t>32796</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7231,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7251,12 +6568,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>13916</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7266,12 +6583,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7286,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20857</t>
+          <t>20588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41699</t>
+          <t>42439</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7301,12 +6618,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41662</t>
+          <t>42122</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67424</t>
+          <t>67695</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7344,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7364,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14474</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7379,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7399,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49641</t>
+          <t>49089</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78196</t>
+          <t>79077</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7414,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44852</t>
+          <t>43432</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71408</t>
+          <t>70872</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7457,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7477,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21358</t>
+          <t>22572</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7492,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7512,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57188</t>
+          <t>56552</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88695</t>
+          <t>87042</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7527,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55519</t>
+          <t>54125</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83150</t>
+          <t>82533</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7570,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7590,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26498</t>
+          <t>26673</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43126</t>
+          <t>42787</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7605,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7625,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86692</t>
+          <t>86355</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118689</t>
+          <t>119817</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7640,12 +6957,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55498</t>
+          <t>54885</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86874</t>
+          <t>85271</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7800,12 +7117,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7820,12 +7137,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50624</t>
+          <t>49255</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80226</t>
+          <t>77901</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7835,12 +7152,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7855,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111948</t>
+          <t>111534</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>153724</t>
+          <t>154363</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7870,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75312</t>
+          <t>76246</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>108943</t>
+          <t>111934</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7913,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7933,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>64294</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>93717</t>
+          <t>94593</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7948,12 +7265,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7968,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>148536</t>
+          <t>147854</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>193226</t>
+          <t>197355</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7983,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>106983</t>
+          <t>106762</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>145833</t>
+          <t>146407</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8026,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8046,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66232</t>
+          <t>68162</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>98650</t>
+          <t>101030</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8061,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8081,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>184213</t>
+          <t>184829</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>232864</t>
+          <t>235278</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8096,12 +7413,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>86142</t>
+          <t>87972</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124618</t>
+          <t>125551</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8139,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8159,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57004</t>
+          <t>54819</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87654</t>
+          <t>85423</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8174,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8194,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152511</t>
+          <t>153763</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>202112</t>
+          <t>201365</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8209,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>81669</t>
+          <t>81571</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>115480</t>
+          <t>117030</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8252,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8272,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58962</t>
+          <t>58230</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>92490</t>
+          <t>89536</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8287,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8307,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>148534</t>
+          <t>147238</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>195585</t>
+          <t>195349</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8322,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>29640</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52901</t>
+          <t>54276</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8482,12 +7799,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8502,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20382</t>
+          <t>20729</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41317</t>
+          <t>41183</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8517,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8537,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>55974</t>
+          <t>55538</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>87295</t>
+          <t>87226</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8552,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30852</t>
+          <t>29335</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>54809</t>
+          <t>53737</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8595,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8615,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24667</t>
+          <t>24165</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>45330</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8630,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8650,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>62521</t>
+          <t>61698</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>92868</t>
+          <t>93508</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8665,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30169</t>
+          <t>30611</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55053</t>
+          <t>55006</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8708,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8728,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>45789</t>
+          <t>48202</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>71947</t>
+          <t>73784</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8743,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8763,12 +8080,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>84008</t>
+          <t>85054</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>119860</t>
+          <t>118431</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8778,12 +8095,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21331</t>
+          <t>21242</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43609</t>
+          <t>43416</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8821,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8841,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32506</t>
+          <t>32870</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>55726</t>
+          <t>56401</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8856,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8876,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>60678</t>
+          <t>60113</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>92613</t>
+          <t>92596</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8891,7 +8208,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -8919,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>28323</t>
+          <t>29008</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>51016</t>
+          <t>52045</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8934,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8954,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>21515</t>
+          <t>21941</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42595</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8969,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8989,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>55876</t>
+          <t>55842</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>85271</t>
+          <t>85851</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9004,12 +8321,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -9129,7 +8446,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9139,107 +8456,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>165</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>181453</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156755</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>207443</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>154</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155972</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135196</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>181123</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>319</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>337425</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>306061</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>378696</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -9252,107 +8569,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>209</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>224891</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197332</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>254758</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>187</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>188822</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>164639</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214527</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>396</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>413714</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>380589</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>455167</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -9365,107 +8682,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>341</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>363562</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332339</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>397845</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>263</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>264777</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>236129</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>295059</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>604</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>628339</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>584790</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>673145</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -9478,107 +8795,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>276</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>297358</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>268688</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>329628</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>188</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>191571</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167644</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>217067</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>464</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>488929</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>448147</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>531584</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -9591,107 +8908,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>332</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>355058</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>321071</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>389656</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>220</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>235076</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>206294</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>261563</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>552</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>590134</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>544197</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>633325</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -9704,804 +9021,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>181453</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>156014</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>209125</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>12,76%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>10,97%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>14,7%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>155972</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>132511</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>179855</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>15,05%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>12,79%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>337425</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>303457</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>373082</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>15,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>224891</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>199302</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>253631</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>14,01%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>17,83%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>188822</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>162214</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>213138</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>18,22%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>15,65%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>413714</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>375918</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>447944</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>15,29%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>18,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>363562</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>330543</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>396966</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>25,56%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>23,24%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>27,91%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>264777</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>236734</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>293670</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>25,55%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>28,34%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>628339</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>586006</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>675756</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>25,56%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>23,84%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>27,49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>297358</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>268041</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>330344</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>20,91%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>18,85%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>23,23%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>191571</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>167313</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>215755</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>16,15%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>20,82%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>488929</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>450131</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>532199</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>19,89%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>18,31%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>355058</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>324521</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>390279</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>24,96%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>22,82%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>27,44%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>235076</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>209323</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>261874</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>22,69%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>20,2%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>25,27%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>590134</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>546976</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>634815</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>24,0%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>25,82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2335</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>

--- a/data/trans_orig/P6710-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6710-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26733</t>
+          <t>27425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26873</t>
+          <t>27441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25343</t>
+          <t>25609</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48495</t>
+          <t>48413</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>11254</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28927</t>
+          <t>29258</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12609</t>
+          <t>11952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31252</t>
+          <t>29371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>26929</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51873</t>
+          <t>52874</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38543</t>
+          <t>39036</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65802</t>
+          <t>66430</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>29417</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52315</t>
+          <t>53505</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72923</t>
+          <t>73554</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>110110</t>
+          <t>108756</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55316</t>
+          <t>55294</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86006</t>
+          <t>84881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19057</t>
+          <t>20220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39637</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82720</t>
+          <t>81856</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117742</t>
+          <t>119893</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>127992</t>
+          <t>127849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163873</t>
+          <t>162542</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72987</t>
+          <t>73326</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102211</t>
+          <t>101793</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>210618</t>
+          <t>210705</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255307</t>
+          <t>257019</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,9%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20379</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28121</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19802</t>
+          <t>19233</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44193</t>
+          <t>42125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11023</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28747</t>
+          <t>27708</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>22877</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>21323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44486</t>
+          <t>44949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49014</t>
+          <t>47900</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78248</t>
+          <t>79164</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28887</t>
+          <t>27240</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51240</t>
+          <t>51566</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>82889</t>
+          <t>83173</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120437</t>
+          <t>120863</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50828</t>
+          <t>49968</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79510</t>
+          <t>79611</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27705</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50424</t>
+          <t>49554</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84666</t>
+          <t>83145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121997</t>
+          <t>119072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82034</t>
+          <t>82933</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116715</t>
+          <t>117763</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44437</t>
+          <t>44927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70568</t>
+          <t>71826</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134792</t>
+          <t>134915</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>178510</t>
+          <t>178802</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28370</t>
+          <t>27991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16073</t>
+          <t>15529</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37649</t>
+          <t>35047</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24344</t>
+          <t>23874</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12134</t>
+          <t>11479</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13138</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29498</t>
+          <t>30994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36528</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63291</t>
+          <t>61000</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26029</t>
+          <t>27163</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51492</t>
+          <t>52672</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>81036</t>
+          <t>81057</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42608</t>
+          <t>43223</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68907</t>
+          <t>68238</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19405</t>
+          <t>18622</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52206</t>
+          <t>52851</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80826</t>
+          <t>81868</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126969</t>
+          <t>127470</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160580</t>
+          <t>160492</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59686</t>
+          <t>59573</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80265</t>
+          <t>80318</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>193724</t>
+          <t>195873</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>232036</t>
+          <t>234794</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>60,18%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49319</t>
+          <t>49074</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79681</t>
+          <t>79463</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39001</t>
+          <t>38653</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65269</t>
+          <t>65320</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93368</t>
+          <t>93899</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>135140</t>
+          <t>134553</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34852</t>
+          <t>32591</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61177</t>
+          <t>60455</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25143</t>
+          <t>24323</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49158</t>
+          <t>47202</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63519</t>
+          <t>63648</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>100937</t>
+          <t>99048</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>80209</t>
+          <t>82021</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>119379</t>
+          <t>117454</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>41449</t>
+          <t>40547</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>68739</t>
+          <t>67991</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>128998</t>
+          <t>131062</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>173921</t>
+          <t>175029</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65981</t>
+          <t>67054</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>100457</t>
+          <t>99989</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56355</t>
+          <t>57456</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86512</t>
+          <t>86483</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130558</t>
+          <t>130962</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>175468</t>
+          <t>174883</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>112007</t>
+          <t>110962</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>150867</t>
+          <t>150499</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,49 +3244,49 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>35,76%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>90496</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>74198</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>107485</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>30,18%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>24,75%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>35,85%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>90496</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>75246</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>108258</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>30,18%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>25,1%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>36,11%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>213</t>
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>196307</t>
+          <t>198950</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>249509</t>
+          <t>247937</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19466</t>
+          <t>19832</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>39877</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21479</t>
+          <t>20813</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41441</t>
+          <t>41965</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>45103</t>
+          <t>46310</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>74744</t>
+          <t>74385</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25181</t>
+          <t>25441</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>11839</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28734</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>24488</t>
+          <t>23832</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>46776</t>
+          <t>46860</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23810</t>
+          <t>24802</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45022</t>
+          <t>45861</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>19350</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>41107</t>
+          <t>40206</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>48309</t>
+          <t>49173</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>77383</t>
+          <t>79465</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21194</t>
+          <t>20381</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>40858</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>28934</t>
+          <t>28602</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>50982</t>
+          <t>52293</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>55964</t>
+          <t>54619</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>87760</t>
+          <t>85943</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31953</t>
+          <t>31773</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>53649</t>
+          <t>54085</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>43154</t>
+          <t>43541</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>69396</t>
+          <t>70184</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>80407</t>
+          <t>80848</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>114364</t>
+          <t>115247</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>114738</t>
+          <t>117612</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>162582</t>
+          <t>163242</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>102976</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>145822</t>
+          <t>142747</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>231854</t>
+          <t>230016</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>293419</t>
+          <t>295208</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>90642</t>
+          <t>92345</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>135581</t>
+          <t>134757</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>74131</t>
+          <t>74576</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>112108</t>
+          <t>113999</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>176266</t>
+          <t>175011</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>234070</t>
+          <t>233128</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>265133</t>
+          <t>261695</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>325211</t>
+          <t>323087</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>152244</t>
+          <t>154541</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>203388</t>
+          <t>202533</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>433235</t>
+          <t>429307</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>515575</t>
+          <t>514697</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>269276</t>
+          <t>270920</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>333028</t>
+          <t>334641</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>162389</t>
+          <t>162682</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>211832</t>
+          <t>216078</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>449582</t>
+          <t>452735</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>533129</t>
+          <t>531013</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>529498</t>
+          <t>525793</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>602581</t>
+          <t>599413</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>333069</t>
+          <t>331589</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>393339</t>
+          <t>392868</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>876157</t>
+          <t>878083</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>973936</t>
+          <t>978907</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>17237</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39331</t>
+          <t>40259</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25300</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48470</t>
+          <t>48105</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49254</t>
+          <t>48311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79636</t>
+          <t>78625</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20576</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41124</t>
+          <t>44622</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>25424</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48094</t>
+          <t>47769</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52142</t>
+          <t>50686</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81564</t>
+          <t>81649</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63211</t>
+          <t>61336</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94743</t>
+          <t>93287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51579</t>
+          <t>52350</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>78227</t>
+          <t>79294</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>121920</t>
+          <t>122481</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>164651</t>
+          <t>162960</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40018</t>
+          <t>40950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67507</t>
+          <t>69780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32185</t>
+          <t>31467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59501</t>
+          <t>59707</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91050</t>
+          <t>94289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74903</t>
+          <t>73920</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>106833</t>
+          <t>106122</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44257</t>
+          <t>44641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>71461</t>
+          <t>70925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>125322</t>
+          <t>126327</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167030</t>
+          <t>169779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>19795</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41401</t>
+          <t>42224</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17691</t>
+          <t>17231</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36896</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41831</t>
+          <t>42103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72698</t>
+          <t>71602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28631</t>
+          <t>27967</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53243</t>
+          <t>53350</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23695</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>44564</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56583</t>
+          <t>56896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89769</t>
+          <t>89052</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50547</t>
+          <t>48970</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>79131</t>
+          <t>78143</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38850</t>
+          <t>39477</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63468</t>
+          <t>62321</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>97282</t>
+          <t>97254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133779</t>
+          <t>132671</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39321</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64450</t>
+          <t>65490</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6092,47 +6092,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>40752</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30479</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>53179</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>21,54%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>16,11%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>26,41%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>40752</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>30008</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>52351</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>21,54%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>15,86%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75689</t>
+          <t>74992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>110767</t>
+          <t>108665</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47951</t>
+          <t>47292</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>75662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27829</t>
+          <t>28144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50246</t>
+          <t>51146</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81826</t>
+          <t>82735</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>117182</t>
+          <t>119513</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,59%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25039</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>28799</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32796</t>
+          <t>33973</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13916</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20588</t>
+          <t>20393</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42439</t>
+          <t>41754</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42122</t>
+          <t>42639</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67695</t>
+          <t>67736</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49089</t>
+          <t>49604</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79077</t>
+          <t>78398</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43432</t>
+          <t>43490</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70872</t>
+          <t>71767</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22572</t>
+          <t>22106</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56552</t>
+          <t>57822</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87042</t>
+          <t>87140</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54125</t>
+          <t>54706</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82533</t>
+          <t>82814</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26673</t>
+          <t>27295</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42787</t>
+          <t>43887</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86355</t>
+          <t>87796</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>119817</t>
+          <t>119292</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,94%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54885</t>
+          <t>55638</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85271</t>
+          <t>86642</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49255</t>
+          <t>49287</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77901</t>
+          <t>76785</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111534</t>
+          <t>111102</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>154363</t>
+          <t>152549</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76246</t>
+          <t>75923</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>111934</t>
+          <t>110202</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>62729</t>
+          <t>63019</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>94593</t>
+          <t>94592</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>147854</t>
+          <t>146800</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>197355</t>
+          <t>194126</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>106762</t>
+          <t>108625</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>146407</t>
+          <t>147091</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>68162</t>
+          <t>66700</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>101030</t>
+          <t>98847</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>184829</t>
+          <t>183724</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>235278</t>
+          <t>233595</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87972</t>
+          <t>86855</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125551</t>
+          <t>123367</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54819</t>
+          <t>56664</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85423</t>
+          <t>86615</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>153763</t>
+          <t>151786</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>201365</t>
+          <t>199316</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>81571</t>
+          <t>80932</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>117030</t>
+          <t>116120</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58230</t>
+          <t>58741</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89536</t>
+          <t>90812</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>147238</t>
+          <t>149084</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>195349</t>
+          <t>194572</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29640</t>
+          <t>30035</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54276</t>
+          <t>53406</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20729</t>
+          <t>21146</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41183</t>
+          <t>41749</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>55538</t>
+          <t>56140</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>87226</t>
+          <t>86307</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29335</t>
+          <t>30255</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>53737</t>
+          <t>55281</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24165</t>
+          <t>24891</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45330</t>
+          <t>45243</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7967,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>61698</t>
+          <t>60938</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>93508</t>
+          <t>92669</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30611</t>
+          <t>30802</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55006</t>
+          <t>54545</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>48202</t>
+          <t>46981</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>73784</t>
+          <t>71461</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>85054</t>
+          <t>83610</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>118431</t>
+          <t>118287</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,21%</t>
         </is>
       </c>
     </row>
@@ -8123,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43416</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8158,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32870</t>
+          <t>33250</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>56401</t>
+          <t>56378</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>60113</t>
+          <t>60986</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>92596</t>
+          <t>90981</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -8236,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29008</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>52045</t>
+          <t>50902</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>21941</t>
+          <t>22103</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41939</t>
+          <t>41503</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>55842</t>
+          <t>55953</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>85851</t>
+          <t>86423</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>156755</t>
+          <t>155977</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>207443</t>
+          <t>209313</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>135196</t>
+          <t>134500</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>181123</t>
+          <t>180462</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>306061</t>
+          <t>305012</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>378696</t>
+          <t>374391</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>197332</t>
+          <t>195696</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>254758</t>
+          <t>252340</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>164639</t>
+          <t>163901</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>214527</t>
+          <t>214012</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>380589</t>
+          <t>381008</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>455167</t>
+          <t>453520</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -8692,12 +8692,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>332339</t>
+          <t>331834</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>397845</t>
+          <t>400174</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>236129</t>
+          <t>237655</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>295059</t>
+          <t>292264</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>584790</t>
+          <t>577604</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>673145</t>
+          <t>668544</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,19%</t>
         </is>
       </c>
     </row>
@@ -8805,12 +8805,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>268688</t>
+          <t>267259</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>329628</t>
+          <t>328269</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>167644</t>
+          <t>169997</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>217067</t>
+          <t>218580</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>448147</t>
+          <t>448933</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>531584</t>
+          <t>531630</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>321071</t>
+          <t>323428</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>389656</t>
+          <t>393283</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>206294</t>
+          <t>206531</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>261563</t>
+          <t>261965</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>544197</t>
+          <t>547435</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>633325</t>
+          <t>636080</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
